--- a/Thu_Kha_Thi/notebooks/ket_qua_do_nhay/bang_do_nhay.xlsx
+++ b/Thu_Kha_Thi/notebooks/ket_qua_do_nhay/bang_do_nhay.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="B1 Mo ta 1999-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B2 Kiem thu nguoc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1 Mo ta 1999-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2 Kiem thu nguoc" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,12 +462,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>240.412</t>
+          <t>240.409</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.726 / 240.412 = 27,75%</t>
+          <t>66.722 / 240.409 = 27,75%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>877 / 66.726 = 1,31%</t>
+          <t>877 / 66.722 = 1,31%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>240.412</t>
+          <t>240.409</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>65.758 / 240.412 = 27,35%</t>
+          <t>65.754 / 240.409 = 27,35%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>868 / 65.758 = 1,32%</t>
+          <t>868 / 65.754 = 1,32%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>174.807</t>
+          <t>174.803</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>62.883 / 174.807 = 35,97%</t>
+          <t>62.879 / 174.803 = 35,97%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>843 / 62.883 = 1,34%</t>
+          <t>843 / 62.879 = 1,34%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>240.412</t>
+          <t>240.409</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>69.738 / 240.412 = 29,01%</t>
+          <t>69.734 / 240.409 = 29,01%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.050 / 69.738 = 1,51%</t>
+          <t>1.050 / 69.734 = 1,51%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>174.807</t>
+          <t>174.803</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.879 / 174.807 = 37,11%</t>
+          <t>64.875 / 174.803 = 37,11%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>906 / 64.879 = 1,40%</t>
+          <t>906 / 64.875 = 1,40%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42.686 / 147.313 = 28,98%</t>
+          <t>42.685 / 147.313 = 28,98%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.225 / 147.313 = 28,66%</t>
+          <t>42.224 / 147.313 = 28,66%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40.623 / 107.701 = 37,72%</t>
+          <t>40.622 / 107.700 = 37,72%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>45.341 / 147.313 = 30,78%</t>
+          <t>45.340 / 147.313 = 30,78%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.411 / 107.701 = 39,38%</t>
+          <t>42.410 / 107.700 = 39,38%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.663 / 186.756 = 28,20%</t>
+          <t>52.662 / 186.756 = 28,20%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>51.924 / 186.756 = 27,80%</t>
+          <t>51.923 / 186.756 = 27,80%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>49.694 / 135.158 = 36,77%</t>
+          <t>49.693 / 135.157 = 36,77%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>55.341 / 186.756 = 29,63%</t>
+          <t>55.340 / 186.756 = 29,63%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>51.496 / 135.158 = 38,10%</t>
+          <t>51.495 / 135.157 = 38,10%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>58.134 / 209.623 = 27,73%</t>
+          <t>58.133 / 209.623 = 27,73%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>57.288 / 209.623 = 27,33%</t>
+          <t>57.287 / 209.623 = 27,33%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>54.861 / 152.155 = 36,06%</t>
+          <t>54.860 / 152.154 = 36,06%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>60.901 / 209.623 = 29,05%</t>
+          <t>60.900 / 209.623 = 29,05%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>56.736 / 152.155 = 37,29%</t>
+          <t>56.735 / 152.154 = 37,29%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
